--- a/artfynd/A 11018-2022 artfynd.xlsx
+++ b/artfynd/A 11018-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11018-2022 artfynd.xlsx
+++ b/artfynd/A 11018-2022 artfynd.xlsx
@@ -675,57 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99099137</v>
+        <v>99101222</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spill, Vg</t>
+          <t>Udden Dammtorp, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478405.8883922836</v>
+        <v>478550</v>
       </c>
       <c r="R2" t="n">
-        <v>6515654.068895391</v>
+        <v>6515331</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99101222</v>
+        <v>99099137</v>
       </c>
       <c r="B3" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,41 +798,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Udden Dammtorp, Vg</t>
+          <t>Spill, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478549.5323261502</v>
+        <v>478405</v>
       </c>
       <c r="R3" t="n">
-        <v>6515331.294906232</v>
+        <v>6515655</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +880,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11018-2022 artfynd.xlsx
+++ b/artfynd/A 11018-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99101222</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,8 +905,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99099137</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>